--- a/product_selector_out/STM32L4x2.xlsx
+++ b/product_selector_out/STM32L4x2.xlsx
@@ -1240,7 +1240,7 @@
       </c>
       <c r="AW12" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX12" s="4" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="AW13" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX13" s="4" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="AW14" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX14" s="4" t="inlineStr">
@@ -2221,7 +2221,7 @@
       </c>
       <c r="AW15" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX15" s="4" t="inlineStr">
@@ -2548,7 +2548,7 @@
       </c>
       <c r="AW16" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX16" s="4" t="inlineStr">
@@ -2875,7 +2875,7 @@
       </c>
       <c r="AW17" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX17" s="4" t="inlineStr">
@@ -3202,7 +3202,7 @@
       </c>
       <c r="AW18" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX18" s="4" t="inlineStr">
@@ -3529,7 +3529,7 @@
       </c>
       <c r="AW19" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX19" s="4" t="inlineStr">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="AW20" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX20" s="4" t="inlineStr">
@@ -4183,7 +4183,7 @@
       </c>
       <c r="AW21" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX21" s="4" t="inlineStr">
@@ -4510,7 +4510,7 @@
       </c>
       <c r="AW22" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX22" s="4" t="inlineStr">
@@ -4837,7 +4837,7 @@
       </c>
       <c r="AW23" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX23" s="4" t="inlineStr">
@@ -5164,7 +5164,7 @@
       </c>
       <c r="AW24" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX24" s="4" t="inlineStr">
@@ -5491,7 +5491,7 @@
       </c>
       <c r="AW25" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX25" s="4" t="inlineStr">
@@ -5818,7 +5818,7 @@
       </c>
       <c r="AW26" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX26" s="4" t="inlineStr">
@@ -6145,7 +6145,7 @@
       </c>
       <c r="AW27" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX27" s="4" t="inlineStr">
@@ -6472,7 +6472,7 @@
       </c>
       <c r="AW28" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX28" s="4" t="inlineStr">
@@ -6799,7 +6799,7 @@
       </c>
       <c r="AW29" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX29" s="4" t="inlineStr">
@@ -7126,7 +7126,7 @@
       </c>
       <c r="AW30" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX30" s="4" t="inlineStr">
@@ -7453,7 +7453,7 @@
       </c>
       <c r="AW31" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX31" s="4" t="inlineStr">
@@ -7780,7 +7780,7 @@
       </c>
       <c r="AW32" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX32" s="4" t="inlineStr">
@@ -8107,7 +8107,7 @@
       </c>
       <c r="AW33" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX33" s="4" t="inlineStr">
@@ -8434,7 +8434,7 @@
       </c>
       <c r="AW34" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX34" s="4" t="inlineStr">
@@ -8761,7 +8761,7 @@
       </c>
       <c r="AW35" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX35" s="4" t="inlineStr">
@@ -9687,9 +9687,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW12" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW12" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX12" s="7" t="inlineStr">
@@ -10014,9 +10014,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW13" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW13" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX13" s="7" t="inlineStr">
@@ -10341,9 +10341,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW14" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW14" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX14" s="7" t="inlineStr">
@@ -10668,9 +10668,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW15" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW15" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX15" s="7" t="inlineStr">
@@ -10995,9 +10995,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW16" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW16" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX16" s="7" t="inlineStr">
@@ -11322,9 +11322,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW17" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW17" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX17" s="7" t="inlineStr">
@@ -11649,9 +11649,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW18" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW18" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX18" s="7" t="inlineStr">
@@ -11976,9 +11976,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW19" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW19" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX19" s="7" t="inlineStr">
@@ -12303,9 +12303,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW20" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW20" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX20" s="7" t="inlineStr">
@@ -12630,9 +12630,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW21" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW21" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX21" s="7" t="inlineStr">
@@ -12957,9 +12957,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW22" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW22" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX22" s="7" t="inlineStr">
@@ -13284,9 +13284,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW23" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW23" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX23" s="7" t="inlineStr">
@@ -13611,9 +13611,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW24" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW24" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX24" s="7" t="inlineStr">
@@ -13938,9 +13938,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW25" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW25" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX25" s="7" t="inlineStr">
@@ -14265,9 +14265,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW26" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW26" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX26" s="7" t="inlineStr">
@@ -14592,9 +14592,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW27" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW27" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX27" s="7" t="inlineStr">
@@ -14919,9 +14919,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW28" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW28" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX28" s="7" t="inlineStr">
@@ -15246,9 +15246,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW29" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW29" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX29" s="7" t="inlineStr">
@@ -15573,9 +15573,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW30" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW30" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX30" s="7" t="inlineStr">
@@ -15900,9 +15900,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW31" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW31" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX31" s="7" t="inlineStr">
@@ -16227,9 +16227,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW32" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW32" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX32" s="7" t="inlineStr">
@@ -16554,9 +16554,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW33" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW33" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX33" s="7" t="inlineStr">
@@ -16881,9 +16881,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW34" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW34" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX34" s="7" t="inlineStr">
@@ -17208,9 +17208,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW35" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW35" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX35" s="7" t="inlineStr">
@@ -17309,7 +17309,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D82"/>
+  <dimension ref="A1:D106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -17387,12 +17387,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>STM32L412KB</t>
+          <t>STM32L442KC</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -17402,7 +17402,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -17414,7 +17414,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -17431,12 +17431,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>STM32L422KB</t>
+          <t>STM32L412KB</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -17446,19 +17446,19 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Table 2. STM32L422xx family device features and peripheral counts lists LQFP32, UFQFPN32 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>STM32L422KB</t>
+          <t>STM32L412KB</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -17468,7 +17468,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Table 2. STM32L422xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -17480,7 +17480,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -17490,19 +17490,19 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
+          <t>Table 2. STM32L422xx family device features and peripheral counts lists LQFP32, UFQFPN32 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>STM32L462CE</t>
+          <t>STM32L422KB</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Other timer functions</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -17512,19 +17512,19 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Table 1. STM32L462xx family device features and peripheral counts lists LQFP48, UFQFPN48 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 2. STM32L422xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>STM32L462CE</t>
+          <t>STM32L422KB</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -17534,19 +17534,19 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 1), and the table does not say which timers the variant omits</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>STM32L462CE</t>
+          <t>STM32L422KB</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -17556,7 +17556,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 1), and the table does not say which timers the variant omits</t>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
@@ -17568,7 +17568,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -17578,7 +17578,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Table 1. STM32L462xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 1. STM32L462xx family device features and peripheral counts lists LQFP48, UFQFPN48 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
@@ -17590,7 +17590,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -17600,19 +17600,19 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
+          <t>Table 10. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 1), and the table does not say which timers the variant omits</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>STM32L412C8</t>
+          <t>STM32L462CE</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -17622,19 +17622,19 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 10. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 1), and the table does not say which timers the variant omits</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>STM32L412C8</t>
+          <t>STM32L462CE</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Other timer functions</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -17644,19 +17644,19 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 1. STM32L462xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>STM32L412R8</t>
+          <t>STM32L462CE</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -17666,19 +17666,19 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 22. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>STM32L412R8</t>
+          <t>STM32L462CE</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -17688,14 +17688,14 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>STM32L412T8</t>
+          <t>STM32L412C8</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -17717,7 +17717,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>STM32L412T8</t>
+          <t>STM32L412C8</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -17739,12 +17739,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>STM32L462RE</t>
+          <t>STM32L412C8</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -17754,14 +17754,14 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Table 1. STM32L462xx family device features and peripheral counts lists LQFP64, UFBGA64, WLCSP64 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>STM32L462RE</t>
+          <t>STM32L412R8</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -17776,14 +17776,14 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 1), and the table does not say which timers the variant omits</t>
+          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>STM32L462RE</t>
+          <t>STM32L412R8</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -17798,19 +17798,19 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 1), and the table does not say which timers the variant omits</t>
+          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>STM32L462RE</t>
+          <t>STM32L412R8</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -17820,19 +17820,19 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Table 1. STM32L462xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>STM32L462RE</t>
+          <t>STM32L412T8</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -17842,19 +17842,19 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
+          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>STM32L452RE</t>
+          <t>STM32L412T8</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -17864,19 +17864,19 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Table 2. STM32L452xx family device features and peripheral counts lists LQFP64, UFBGA64, WLCSP64 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>STM32L452RE</t>
+          <t>STM32L412T8</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -17886,19 +17886,19 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Table 11. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 1), and the table does not say which timers the variant omits</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>STM32L452RE</t>
+          <t>STM32L462RE</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -17908,19 +17908,19 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Table 11. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 1), and the table does not say which timers the variant omits</t>
+          <t>Table 1. STM32L462xx family device features and peripheral counts lists LQFP64, UFBGA64, WLCSP64 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>STM32L452RE</t>
+          <t>STM32L462RE</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -17930,19 +17930,19 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Table 2. STM32L452xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 10. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 1), and the table does not say which timers the variant omits</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>STM32L452RE</t>
+          <t>STM32L462RE</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -17952,19 +17952,19 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
+          <t>Table 10. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 1), and the table does not say which timers the variant omits</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>STM32L432KB</t>
+          <t>STM32L462RE</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Other timer functions</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -17974,19 +17974,19 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Table 1. STM32L432Kx family device features and peripheral counts lists UFQFPN32 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 1. STM32L462xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>STM32L432KB</t>
+          <t>STM32L462RE</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -17996,14 +17996,14 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Table 1. STM32L432Kx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 22. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>STM32L432KB</t>
+          <t>STM32L462RE</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -18018,14 +18018,14 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: -40 to 85 °C / - 40 to 105 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 125 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>STM32L452VE</t>
+          <t>STM32L452RE</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -18040,14 +18040,14 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Table 2. STM32L452xx family device features and peripheral counts lists LQFP100, UFBGA100 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 2. STM32L452xx family device features and peripheral counts lists LQFP64, UFBGA64, WLCSP64 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>STM32L452VE</t>
+          <t>STM32L452RE</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -18069,7 +18069,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>STM32L452VE</t>
+          <t>STM32L452RE</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -18091,7 +18091,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>STM32L452VE</t>
+          <t>STM32L452RE</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -18113,12 +18113,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>STM32L452VE</t>
+          <t>STM32L452RE</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -18128,19 +18128,19 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
+          <t>Table 23. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>STM32L462VE</t>
+          <t>STM32L452RE</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -18150,19 +18150,19 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Table 1. STM32L462xx family device features and peripheral counts lists LQFP100, UFBGA100 for this family; the table gives no key to tie a package to this part</t>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>STM32L462VE</t>
+          <t>STM32L432KB</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -18172,19 +18172,19 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 1), and the table does not say which timers the variant omits</t>
+          <t>Table 1. STM32L432Kx family device features and peripheral counts lists UFQFPN32 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>STM32L462VE</t>
+          <t>STM32L432KB</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Other timer functions</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -18194,19 +18194,19 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 1), and the table does not say which timers the variant omits</t>
+          <t>Table 1. STM32L432Kx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>STM32L462VE</t>
+          <t>STM32L432KB</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -18216,14 +18216,14 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Table 1. STM32L462xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>STM32L462VE</t>
+          <t>STM32L432KB</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -18238,14 +18238,14 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
+          <t>Ambient operating temperature: -40 to 85 °C / - 40 to 105 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 125 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>STM32L422CB</t>
+          <t>STM32L452VE</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -18260,19 +18260,19 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Table 2. STM32L422xx family device features and peripheral counts lists LQFP48, UFQFPN48 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 2. STM32L452xx family device features and peripheral counts lists LQFP100, UFBGA100 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>STM32L422CB</t>
+          <t>STM32L452VE</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -18282,19 +18282,19 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Table 2. STM32L422xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 11. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 1), and the table does not say which timers the variant omits</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>STM32L422CB</t>
+          <t>STM32L452VE</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -18304,19 +18304,19 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
+          <t>Table 11. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 1), and the table does not say which timers the variant omits</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>STM32L452CE</t>
+          <t>STM32L452VE</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Other timer functions</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -18326,19 +18326,19 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Table 2. STM32L452xx family device features and peripheral counts lists LQFP48, UFQFPN48 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 2. STM32L452xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>STM32L452CE</t>
+          <t>STM32L452VE</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -18348,19 +18348,19 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Table 11. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 1), and the table does not say which timers the variant omits</t>
+          <t>Table 23. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>STM32L452CE</t>
+          <t>STM32L452VE</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -18370,19 +18370,19 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Table 11. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 1), and the table does not say which timers the variant omits</t>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>STM32L452CE</t>
+          <t>STM32L462VE</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -18392,19 +18392,19 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Table 2. STM32L452xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 1. STM32L462xx family device features and peripheral counts lists LQFP100, UFBGA100 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>STM32L452CE</t>
+          <t>STM32L462VE</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -18414,19 +18414,19 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
+          <t>Table 10. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 1), and the table does not say which timers the variant omits</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>STM32L422RB</t>
+          <t>STM32L462VE</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -18436,14 +18436,14 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Table 2. STM32L422xx family device features and peripheral counts lists LQFP64, UFBGA64 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 10. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 1), and the table does not say which timers the variant omits</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>STM32L422RB</t>
+          <t>STM32L462VE</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -18458,19 +18458,19 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Table 2. STM32L422xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 1. STM32L462xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>STM32L422RB</t>
+          <t>STM32L462VE</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -18480,19 +18480,19 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
+          <t>Table 22. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>STM32L412RB</t>
+          <t>STM32L462VE</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -18502,19 +18502,19 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>STM32L412RB</t>
+          <t>STM32L422CB</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -18524,19 +18524,19 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 2. STM32L422xx family device features and peripheral counts lists LQFP48, UFQFPN48 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>STM32L452CC</t>
+          <t>STM32L422CB</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Other timer functions</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -18546,19 +18546,19 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Table 2. STM32L452xx family device features and peripheral counts lists LQFP48, UFQFPN48 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 2. STM32L422xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>STM32L452CC</t>
+          <t>STM32L422CB</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -18568,19 +18568,19 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Table 11. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 1), and the table does not say which timers the variant omits</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>STM32L452CC</t>
+          <t>STM32L422CB</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -18590,19 +18590,19 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Table 11. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 1), and the table does not say which timers the variant omits</t>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>STM32L452CC</t>
+          <t>STM32L452CE</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -18612,19 +18612,19 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Table 2. STM32L452xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 2. STM32L452xx family device features and peripheral counts lists LQFP48, UFQFPN48 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>STM32L452CC</t>
+          <t>STM32L452CE</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -18634,19 +18634,19 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
+          <t>Table 11. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 1), and the table does not say which timers the variant omits</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>STM32L412K8</t>
+          <t>STM32L452CE</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -18656,19 +18656,19 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 11. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 1), and the table does not say which timers the variant omits</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>STM32L412K8</t>
+          <t>STM32L452CE</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Other timer functions</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -18678,19 +18678,19 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 2. STM32L452xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>STM32L412TB</t>
+          <t>STM32L452CE</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -18700,19 +18700,19 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 23. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>STM32L412TB</t>
+          <t>STM32L452CE</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -18722,14 +18722,14 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>STM32L432KC</t>
+          <t>STM32L422RB</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -18744,14 +18744,14 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Table 1. STM32L432Kx family device features and peripheral counts lists UFQFPN32 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 2. STM32L422xx family device features and peripheral counts lists LQFP64, UFBGA64 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>STM32L432KC</t>
+          <t>STM32L422RB</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -18766,19 +18766,19 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Table 1. STM32L432Kx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 2. STM32L422xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>STM32L432KC</t>
+          <t>STM32L422RB</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -18788,19 +18788,19 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: -40 to 85 °C / - 40 to 105 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 125 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>STM32L452RC</t>
+          <t>STM32L422RB</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -18810,14 +18810,14 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Table 2. STM32L452xx family device features and peripheral counts lists LQFP64, UFBGA64, WLCSP64 for this family; the table gives no key to tie a package to this part</t>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>STM32L452RC</t>
+          <t>STM32L412RB</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -18832,14 +18832,14 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Table 11. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 1), and the table does not say which timers the variant omits</t>
+          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>STM32L452RC</t>
+          <t>STM32L412RB</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -18854,19 +18854,19 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Table 11. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 1), and the table does not say which timers the variant omits</t>
+          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>STM32L452RC</t>
+          <t>STM32L412RB</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -18876,19 +18876,19 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Table 2. STM32L452xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>STM32L452RC</t>
+          <t>STM32L452CC</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -18898,19 +18898,19 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
+          <t>Table 2. STM32L452xx family device features and peripheral counts lists LQFP48, UFQFPN48 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>STM32L452VC</t>
+          <t>STM32L452CC</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -18920,19 +18920,19 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Table 2. STM32L452xx family device features and peripheral counts lists LQFP100, UFBGA100 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 11. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 1), and the table does not say which timers the variant omits</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>STM32L452VC</t>
+          <t>STM32L452CC</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -18949,12 +18949,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>STM32L452VC</t>
+          <t>STM32L452CC</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Other timer functions</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -18964,19 +18964,19 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Table 11. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 1), and the table does not say which timers the variant omits</t>
+          <t>Table 2. STM32L452xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>STM32L452VC</t>
+          <t>STM32L452CC</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -18986,14 +18986,14 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Table 2. STM32L452xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 23. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>STM32L452VC</t>
+          <t>STM32L452CC</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -19015,7 +19015,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>STM32L412CB</t>
+          <t>STM32L412K8</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -19037,7 +19037,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>STM32L412CB</t>
+          <t>STM32L412K8</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -19059,12 +19059,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>STM32L422TB</t>
+          <t>STM32L412K8</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -19074,19 +19074,19 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Table 2. STM32L422xx family device features and peripheral counts lists WLCSP36 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>STM32L422TB</t>
+          <t>STM32L412TB</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -19096,27 +19096,555 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Table 2. STM32L422xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
+          <t>STM32L412TB</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>STM32L412TB</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Table 21. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>STM32L432KC</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Package</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Table 1. STM32L432Kx family device features and peripheral counts lists UFQFPN32 for this family; the table gives no key to tie a package to this part</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>STM32L432KC</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Other timer functions</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Table 1. STM32L432Kx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>STM32L432KC</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Table 21. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>STM32L432KC</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Operating Temperature (°C) max</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Ambient operating temperature: -40 to 85 °C / - 40 to 105 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 125 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>STM32L452RC</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Package</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Table 2. STM32L452xx family device features and peripheral counts lists LQFP64, UFBGA64, WLCSP64 for this family; the table gives no key to tie a package to this part</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>STM32L452RC</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Table 11. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 1), and the table does not say which timers the variant omits</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>STM32L452RC</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Table 11. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 1), and the table does not say which timers the variant omits</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>STM32L452RC</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Other timer functions</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Table 2. STM32L452xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>STM32L452RC</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Table 23. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>STM32L452RC</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Operating Temperature (°C) max</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>STM32L452VC</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Package</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Table 2. STM32L452xx family device features and peripheral counts lists LQFP100, UFBGA100 for this family; the table gives no key to tie a package to this part</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>STM32L452VC</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Table 11. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 1), and the table does not say which timers the variant omits</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>STM32L452VC</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Table 11. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 1), and the table does not say which timers the variant omits</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>STM32L452VC</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Other timer functions</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Table 2. STM32L452xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>STM32L452VC</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Table 23. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>STM32L452VC</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Operating Temperature (°C) max</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>STM32L412CB</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>STM32L412CB</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>STM32L412CB</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Table 21. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
           <t>STM32L422TB</t>
         </is>
       </c>
-      <c r="B82" t="inlineStr">
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Package</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Table 2. STM32L422xx family device features and peripheral counts lists WLCSP36 for this family; the table gives no key to tie a package to this part</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>STM32L422TB</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Other timer functions</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Table 2. STM32L422xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>STM32L422TB</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Table 21. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>STM32L422TB</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
         <is>
           <t>Operating Temperature (°C) max</t>
         </is>
       </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
         <is>
           <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
         </is>

--- a/product_selector_out/STM32L4x2.xlsx
+++ b/product_selector_out/STM32L4x2.xlsx
@@ -1739,7 +1739,7 @@
       </c>
       <c r="R14" s="4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="S14" s="4" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="R15" s="4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="S15" s="4" t="inlineStr">
@@ -3374,7 +3374,7 @@
       </c>
       <c r="R19" s="4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="S19" s="4" t="inlineStr">
@@ -3701,7 +3701,7 @@
       </c>
       <c r="R20" s="4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="S20" s="4" t="inlineStr">
@@ -3721,7 +3721,7 @@
       </c>
       <c r="V20" s="4" t="inlineStr">
         <is>
-          <t>15, 16</t>
+          <t>16</t>
         </is>
       </c>
       <c r="W20" s="4" t="inlineStr">
@@ -4028,7 +4028,7 @@
       </c>
       <c r="R21" s="4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="S21" s="4" t="inlineStr">
@@ -4355,7 +4355,7 @@
       </c>
       <c r="R22" s="4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="S22" s="4" t="inlineStr">
@@ -4682,7 +4682,7 @@
       </c>
       <c r="R23" s="4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="S23" s="4" t="inlineStr">
@@ -5009,7 +5009,7 @@
       </c>
       <c r="R24" s="4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="S24" s="4" t="inlineStr">
@@ -5336,7 +5336,7 @@
       </c>
       <c r="R25" s="4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="S25" s="4" t="inlineStr">
@@ -5663,7 +5663,7 @@
       </c>
       <c r="R26" s="4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="S26" s="4" t="inlineStr">
@@ -6317,7 +6317,7 @@
       </c>
       <c r="R28" s="4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="S28" s="4" t="inlineStr">
@@ -7298,7 +7298,7 @@
       </c>
       <c r="R31" s="4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="S31" s="4" t="inlineStr">
@@ -7625,7 +7625,7 @@
       </c>
       <c r="R32" s="4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="S32" s="4" t="inlineStr">
@@ -7952,7 +7952,7 @@
       </c>
       <c r="R33" s="4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="S33" s="4" t="inlineStr">
@@ -8606,7 +8606,7 @@
       </c>
       <c r="R35" s="4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="S35" s="4" t="inlineStr">
@@ -10201,14 +10201,14 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="U14" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="V14" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="U14" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="V14" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="W14" s="8" t="inlineStr">
@@ -10513,29 +10513,29 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R15" s="9" t="inlineStr">
+      <c r="R15" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
+        </is>
+      </c>
+      <c r="S15" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
+        </is>
+      </c>
+      <c r="T15" s="9" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="S15" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="T15" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="U15" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="V15" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="U15" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="V15" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="W15" s="8" t="inlineStr">
@@ -10558,9 +10558,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA15" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA15" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB15" s="6" t="inlineStr">
@@ -10618,9 +10618,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM15" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AM15" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AN15" s="6" t="inlineStr">
@@ -11821,29 +11821,29 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R19" s="9" t="inlineStr">
+      <c r="R19" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
+        </is>
+      </c>
+      <c r="S19" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
+        </is>
+      </c>
+      <c r="T19" s="9" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="S19" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="T19" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="U19" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="V19" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="U19" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="V19" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="W19" s="8" t="inlineStr">
@@ -11866,9 +11866,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA19" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA19" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB19" s="6" t="inlineStr">
@@ -11926,9 +11926,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM19" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AM19" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AN19" s="6" t="inlineStr">
@@ -12148,29 +12148,29 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R20" s="9" t="inlineStr">
+      <c r="R20" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
+        </is>
+      </c>
+      <c r="S20" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
+        </is>
+      </c>
+      <c r="T20" s="9" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="S20" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="T20" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="U20" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="V20" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="U20" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="V20" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="W20" s="8" t="inlineStr">
@@ -12193,9 +12193,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA20" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA20" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB20" s="6" t="inlineStr">
@@ -12253,9 +12253,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM20" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AM20" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AN20" s="6" t="inlineStr">
@@ -12490,14 +12490,14 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="U21" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="V21" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="U21" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="V21" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="W21" s="8" t="inlineStr">
@@ -12520,9 +12520,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA21" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA21" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB21" s="6" t="inlineStr">
@@ -12802,29 +12802,29 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R22" s="9" t="inlineStr">
+      <c r="R22" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
+        </is>
+      </c>
+      <c r="S22" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
+        </is>
+      </c>
+      <c r="T22" s="9" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="S22" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="T22" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="U22" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="V22" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="U22" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="V22" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="W22" s="8" t="inlineStr">
@@ -12847,9 +12847,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA22" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA22" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB22" s="6" t="inlineStr">
@@ -12907,9 +12907,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM22" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AM22" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AN22" s="6" t="inlineStr">
@@ -13129,29 +13129,29 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R23" s="9" t="inlineStr">
+      <c r="R23" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
+        </is>
+      </c>
+      <c r="S23" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
+        </is>
+      </c>
+      <c r="T23" s="9" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="S23" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="T23" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="U23" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="V23" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="U23" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="V23" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="W23" s="8" t="inlineStr">
@@ -13174,9 +13174,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA23" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA23" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB23" s="6" t="inlineStr">
@@ -13234,9 +13234,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM23" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AM23" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AN23" s="6" t="inlineStr">
@@ -13471,14 +13471,14 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="U24" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="V24" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="U24" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="V24" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="W24" s="8" t="inlineStr">
@@ -13783,29 +13783,29 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R25" s="9" t="inlineStr">
+      <c r="R25" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
+        </is>
+      </c>
+      <c r="S25" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
+        </is>
+      </c>
+      <c r="T25" s="9" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="S25" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="T25" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="U25" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="V25" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="U25" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="V25" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="W25" s="8" t="inlineStr">
@@ -13828,9 +13828,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA25" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA25" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB25" s="6" t="inlineStr">
@@ -13888,9 +13888,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM25" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AM25" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AN25" s="6" t="inlineStr">
@@ -14125,14 +14125,14 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="U26" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="V26" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="U26" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="V26" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="W26" s="8" t="inlineStr">
@@ -14764,29 +14764,29 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R28" s="9" t="inlineStr">
+      <c r="R28" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
+        </is>
+      </c>
+      <c r="S28" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
+        </is>
+      </c>
+      <c r="T28" s="9" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="S28" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="T28" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="U28" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="V28" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="U28" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="V28" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="W28" s="8" t="inlineStr">
@@ -14809,9 +14809,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA28" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA28" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB28" s="6" t="inlineStr">
@@ -14869,9 +14869,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM28" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AM28" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AN28" s="6" t="inlineStr">
@@ -15760,14 +15760,14 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="U31" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="V31" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="U31" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="V31" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="W31" s="8" t="inlineStr">
@@ -15790,9 +15790,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA31" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA31" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB31" s="6" t="inlineStr">
@@ -16072,29 +16072,29 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R32" s="9" t="inlineStr">
+      <c r="R32" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
+        </is>
+      </c>
+      <c r="S32" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
+        </is>
+      </c>
+      <c r="T32" s="9" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="S32" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="T32" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="U32" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="V32" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="U32" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="V32" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="W32" s="8" t="inlineStr">
@@ -16117,9 +16117,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA32" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA32" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB32" s="6" t="inlineStr">
@@ -16177,9 +16177,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM32" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AM32" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AN32" s="6" t="inlineStr">
@@ -16399,29 +16399,29 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R33" s="9" t="inlineStr">
+      <c r="R33" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
+        </is>
+      </c>
+      <c r="S33" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
+        </is>
+      </c>
+      <c r="T33" s="9" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="S33" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="T33" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="U33" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="V33" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="U33" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="V33" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="W33" s="8" t="inlineStr">
@@ -16444,9 +16444,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA33" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA33" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB33" s="6" t="inlineStr">
@@ -16504,9 +16504,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM33" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AM33" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AN33" s="6" t="inlineStr">
@@ -17068,14 +17068,14 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="U35" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="V35" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="U35" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="V35" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="W35" s="8" t="inlineStr">
@@ -17309,7 +17309,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D106"/>
+  <dimension ref="A1:D88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -17590,7 +17590,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Other timer functions</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -17600,7 +17600,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 1), and the table does not say which timers the variant omits</t>
+          <t>Table 1. STM32L462xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
@@ -17612,7 +17612,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -17622,7 +17622,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 1), and the table does not say which timers the variant omits</t>
+          <t>Table 22. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -17634,7 +17634,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -17644,19 +17644,19 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Table 1. STM32L462xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>STM32L462CE</t>
+          <t>STM32L412C8</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -17666,19 +17666,19 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Table 22. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>STM32L462CE</t>
+          <t>STM32L412C8</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -17688,7 +17688,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
+          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
@@ -17700,7 +17700,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -17710,19 +17710,19 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>STM32L412C8</t>
+          <t>STM32L412R8</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -17739,12 +17739,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>STM32L412C8</t>
+          <t>STM32L412R8</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -17754,7 +17754,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
@@ -17766,7 +17766,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -17776,19 +17776,19 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>STM32L412R8</t>
+          <t>STM32L412T8</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -17805,12 +17805,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>STM32L412R8</t>
+          <t>STM32L412T8</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -17820,7 +17820,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
@@ -17832,7 +17832,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -17842,19 +17842,19 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>STM32L412T8</t>
+          <t>STM32L462RE</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -17864,19 +17864,19 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 1. STM32L462xx family device features and peripheral counts lists LQFP64, UFBGA64, WLCSP64 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>STM32L412T8</t>
+          <t>STM32L462RE</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Other timer functions</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -17886,7 +17886,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 1. STM32L462xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
@@ -17898,7 +17898,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -17908,7 +17908,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Table 1. STM32L462xx family device features and peripheral counts lists LQFP64, UFBGA64, WLCSP64 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 22. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -17920,7 +17920,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -17930,19 +17930,19 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 1), and the table does not say which timers the variant omits</t>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>STM32L462RE</t>
+          <t>STM32L452RE</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -17952,14 +17952,14 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 1), and the table does not say which timers the variant omits</t>
+          <t>Table 2. STM32L452xx family device features and peripheral counts lists LQFP64, UFBGA64, WLCSP64 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>STM32L462RE</t>
+          <t>STM32L452RE</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -17974,14 +17974,14 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Table 1. STM32L462xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 2. STM32L452xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>STM32L462RE</t>
+          <t>STM32L452RE</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -17996,14 +17996,14 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Table 22. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 23. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>STM32L462RE</t>
+          <t>STM32L452RE</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -18025,7 +18025,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>STM32L452RE</t>
+          <t>STM32L432KB</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -18040,19 +18040,19 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Table 2. STM32L452xx family device features and peripheral counts lists LQFP64, UFBGA64, WLCSP64 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 1. STM32L432Kx family device features and peripheral counts lists UFQFPN32 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>STM32L452RE</t>
+          <t>STM32L432KB</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Other timer functions</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -18062,19 +18062,19 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Table 11. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 1), and the table does not say which timers the variant omits</t>
+          <t>Table 1. STM32L432Kx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>STM32L452RE</t>
+          <t>STM32L432KB</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -18084,19 +18084,19 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Table 11. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 1), and the table does not say which timers the variant omits</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>STM32L452RE</t>
+          <t>STM32L432KB</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -18106,19 +18106,19 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Table 2. STM32L452xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Ambient operating temperature: -40 to 85 °C / - 40 to 105 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 125 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>STM32L452RE</t>
+          <t>STM32L452VE</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -18128,19 +18128,19 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Table 23. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 2. STM32L452xx family device features and peripheral counts lists LQFP100, UFBGA100 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>STM32L452RE</t>
+          <t>STM32L452VE</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Other timer functions</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -18150,19 +18150,19 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
+          <t>Table 2. STM32L452xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>STM32L432KB</t>
+          <t>STM32L452VE</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -18172,19 +18172,19 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Table 1. STM32L432Kx family device features and peripheral counts lists UFQFPN32 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 23. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>STM32L432KB</t>
+          <t>STM32L452VE</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -18194,19 +18194,19 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Table 1. STM32L432Kx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>STM32L432KB</t>
+          <t>STM32L462VE</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -18216,19 +18216,19 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 1. STM32L462xx family device features and peripheral counts lists LQFP100, UFBGA100 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>STM32L432KB</t>
+          <t>STM32L462VE</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Other timer functions</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -18238,19 +18238,19 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: -40 to 85 °C / - 40 to 105 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 125 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
+          <t>Table 1. STM32L462xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>STM32L452VE</t>
+          <t>STM32L462VE</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -18260,19 +18260,19 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Table 2. STM32L452xx family device features and peripheral counts lists LQFP100, UFBGA100 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 22. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>STM32L452VE</t>
+          <t>STM32L462VE</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -18282,19 +18282,19 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Table 11. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 1), and the table does not say which timers the variant omits</t>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>STM32L452VE</t>
+          <t>STM32L422CB</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -18304,14 +18304,14 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Table 11. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 1), and the table does not say which timers the variant omits</t>
+          <t>Table 2. STM32L422xx family device features and peripheral counts lists LQFP48, UFQFPN48 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>STM32L452VE</t>
+          <t>STM32L422CB</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -18326,14 +18326,14 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Table 2. STM32L452xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 2. STM32L422xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>STM32L452VE</t>
+          <t>STM32L422CB</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -18348,14 +18348,14 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Table 23. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>STM32L452VE</t>
+          <t>STM32L422CB</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -18377,7 +18377,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>STM32L462VE</t>
+          <t>STM32L452CE</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -18392,19 +18392,19 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Table 1. STM32L462xx family device features and peripheral counts lists LQFP100, UFBGA100 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 2. STM32L452xx family device features and peripheral counts lists LQFP48, UFQFPN48 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>STM32L462VE</t>
+          <t>STM32L452CE</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Other timer functions</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -18414,19 +18414,19 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 1), and the table does not say which timers the variant omits</t>
+          <t>Table 2. STM32L452xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>STM32L462VE</t>
+          <t>STM32L452CE</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -18436,19 +18436,19 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 1), and the table does not say which timers the variant omits</t>
+          <t>Table 23. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>STM32L462VE</t>
+          <t>STM32L452CE</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -18458,19 +18458,19 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Table 1. STM32L462xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>STM32L462VE</t>
+          <t>STM32L422RB</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -18480,19 +18480,19 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Table 22. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 2. STM32L422xx family device features and peripheral counts lists LQFP64, UFBGA64 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>STM32L462VE</t>
+          <t>STM32L422RB</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Other timer functions</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -18502,19 +18502,19 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
+          <t>Table 2. STM32L422xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>STM32L422CB</t>
+          <t>STM32L422RB</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -18524,19 +18524,19 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Table 2. STM32L422xx family device features and peripheral counts lists LQFP48, UFQFPN48 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>STM32L422CB</t>
+          <t>STM32L422RB</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -18546,19 +18546,19 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Table 2. STM32L422xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>STM32L422CB</t>
+          <t>STM32L412RB</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -18568,19 +18568,19 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>STM32L422CB</t>
+          <t>STM32L412RB</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -18590,19 +18590,19 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
+          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>STM32L452CE</t>
+          <t>STM32L412RB</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -18612,19 +18612,19 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Table 2. STM32L452xx family device features and peripheral counts lists LQFP48, UFQFPN48 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>STM32L452CE</t>
+          <t>STM32L452CC</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -18634,19 +18634,19 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Table 11. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 1), and the table does not say which timers the variant omits</t>
+          <t>Table 2. STM32L452xx family device features and peripheral counts lists LQFP48, UFQFPN48 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>STM32L452CE</t>
+          <t>STM32L452CC</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Other timer functions</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -18656,19 +18656,19 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Table 11. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 1), and the table does not say which timers the variant omits</t>
+          <t>Table 2. STM32L452xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>STM32L452CE</t>
+          <t>STM32L452CC</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -18678,19 +18678,19 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Table 2. STM32L452xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 23. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>STM32L452CE</t>
+          <t>STM32L452CC</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -18700,19 +18700,19 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Table 23. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>STM32L452CE</t>
+          <t>STM32L412K8</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -18722,19 +18722,19 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
+          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>STM32L422RB</t>
+          <t>STM32L412K8</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -18744,19 +18744,19 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Table 2. STM32L422xx family device features and peripheral counts lists LQFP64, UFBGA64 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>STM32L422RB</t>
+          <t>STM32L412K8</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -18766,19 +18766,19 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Table 2. STM32L422xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>STM32L422RB</t>
+          <t>STM32L412TB</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -18788,19 +18788,19 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>STM32L422RB</t>
+          <t>STM32L412TB</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -18810,19 +18810,19 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
+          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>STM32L412RB</t>
+          <t>STM32L412TB</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -18832,19 +18832,19 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>STM32L412RB</t>
+          <t>STM32L432KC</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -18854,19 +18854,19 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 1. STM32L432Kx family device features and peripheral counts lists UFQFPN32 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>STM32L412RB</t>
+          <t>STM32L432KC</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Other timer functions</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -18876,19 +18876,19 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 1. STM32L432Kx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>STM32L452CC</t>
+          <t>STM32L432KC</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -18898,19 +18898,19 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Table 2. STM32L452xx family device features and peripheral counts lists LQFP48, UFQFPN48 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>STM32L452CC</t>
+          <t>STM32L432KC</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -18920,19 +18920,19 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Table 11. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 1), and the table does not say which timers the variant omits</t>
+          <t>Ambient operating temperature: -40 to 85 °C / - 40 to 105 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 125 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>STM32L452CC</t>
+          <t>STM32L452RC</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -18942,14 +18942,14 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Table 11. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 1), and the table does not say which timers the variant omits</t>
+          <t>Table 2. STM32L452xx family device features and peripheral counts lists LQFP64, UFBGA64, WLCSP64 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>STM32L452CC</t>
+          <t>STM32L452RC</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -18971,7 +18971,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>STM32L452CC</t>
+          <t>STM32L452RC</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -18993,7 +18993,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>STM32L452CC</t>
+          <t>STM32L452RC</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -19015,12 +19015,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>STM32L412K8</t>
+          <t>STM32L452VC</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -19030,19 +19030,19 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 2. STM32L452xx family device features and peripheral counts lists LQFP100, UFBGA100 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>STM32L412K8</t>
+          <t>STM32L452VC</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Other timer functions</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -19052,14 +19052,14 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 2. STM32L452xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>STM32L412K8</t>
+          <t>STM32L452VC</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -19074,19 +19074,19 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 23. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>STM32L412TB</t>
+          <t>STM32L452VC</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -19096,19 +19096,19 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>STM32L412TB</t>
+          <t>STM32L412CB</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -19125,12 +19125,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>STM32L412TB</t>
+          <t>STM32L412CB</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -19140,19 +19140,19 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>STM32L432KC</t>
+          <t>STM32L412CB</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -19162,19 +19162,19 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Table 1. STM32L432Kx family device features and peripheral counts lists UFQFPN32 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>STM32L432KC</t>
+          <t>STM32L422TB</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -19184,19 +19184,19 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Table 1. STM32L432Kx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 2. STM32L422xx family device features and peripheral counts lists WLCSP36 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>STM32L432KC</t>
+          <t>STM32L422TB</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Other timer functions</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -19206,19 +19206,19 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 2. STM32L422xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>STM32L432KC</t>
+          <t>STM32L422TB</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -19228,19 +19228,19 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: -40 to 85 °C / - 40 to 105 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 125 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>STM32L452RC</t>
+          <t>STM32L422TB</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -19249,402 +19249,6 @@
         </is>
       </c>
       <c r="D88" t="inlineStr">
-        <is>
-          <t>Table 2. STM32L452xx family device features and peripheral counts lists LQFP64, UFBGA64, WLCSP64 for this family; the table gives no key to tie a package to this part</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>STM32L452RC</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>Table 11. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 1), and the table does not say which timers the variant omits</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>STM32L452RC</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>Table 11. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 1), and the table does not say which timers the variant omits</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>STM32L452RC</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>Other timer functions</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>Table 2. STM32L452xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>STM32L452RC</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>Table 23. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>STM32L452RC</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>Operating Temperature (°C) max</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>STM32L452VC</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>Package</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>Table 2. STM32L452xx family device features and peripheral counts lists LQFP100, UFBGA100 for this family; the table gives no key to tie a package to this part</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>STM32L452VC</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>Table 11. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 1), and the table does not say which timers the variant omits</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>STM32L452VC</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>Table 11. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 1), and the table does not say which timers the variant omits</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>STM32L452VC</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>Other timer functions</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>Table 2. STM32L452xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>STM32L452VC</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>Table 23. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>STM32L452VC</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>Operating Temperature (°C) max</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>STM32L412CB</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>STM32L412CB</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>STM32L412CB</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>STM32L422TB</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>Package</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>Table 2. STM32L422xx family device features and peripheral counts lists WLCSP36 for this family; the table gives no key to tie a package to this part</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>STM32L422TB</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>Other timer functions</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>Table 2. STM32L422xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>STM32L422TB</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>STM32L422TB</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>Operating Temperature (°C) max</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr">
         <is>
           <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
         </is>

--- a/product_selector_out/STM32L4x2.xlsx
+++ b/product_selector_out/STM32L4x2.xlsx
@@ -1844,7 +1844,7 @@
       </c>
       <c r="AM14" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="AN14" s="4" t="inlineStr">
@@ -4133,7 +4133,7 @@
       </c>
       <c r="AM21" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="AN21" s="4" t="inlineStr">
@@ -5114,7 +5114,7 @@
       </c>
       <c r="AM24" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="AN24" s="4" t="inlineStr">
@@ -5768,7 +5768,7 @@
       </c>
       <c r="AM26" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="AN26" s="4" t="inlineStr">
@@ -7403,7 +7403,7 @@
       </c>
       <c r="AM31" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="AN31" s="4" t="inlineStr">
@@ -8711,7 +8711,7 @@
       </c>
       <c r="AM35" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="AN35" s="4" t="inlineStr">
@@ -10291,9 +10291,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM14" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AM14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="AN14" s="6" t="inlineStr">
@@ -10618,9 +10618,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM15" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM15" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN15" s="6" t="inlineStr">
@@ -11926,9 +11926,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM19" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM19" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN19" s="6" t="inlineStr">
@@ -12253,9 +12253,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM20" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM20" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN20" s="6" t="inlineStr">
@@ -12580,9 +12580,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM21" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AM21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="AN21" s="6" t="inlineStr">
@@ -12907,9 +12907,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM22" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM22" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN22" s="6" t="inlineStr">
@@ -13234,9 +13234,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM23" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM23" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN23" s="6" t="inlineStr">
@@ -13561,9 +13561,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM24" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AM24" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="AN24" s="6" t="inlineStr">
@@ -13888,9 +13888,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM25" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM25" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN25" s="6" t="inlineStr">
@@ -14215,9 +14215,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM26" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AM26" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="AN26" s="6" t="inlineStr">
@@ -14869,9 +14869,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM28" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM28" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN28" s="6" t="inlineStr">
@@ -15850,9 +15850,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM31" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AM31" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="AN31" s="6" t="inlineStr">
@@ -16177,9 +16177,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM32" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM32" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN32" s="6" t="inlineStr">
@@ -16504,9 +16504,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM33" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM33" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN33" s="6" t="inlineStr">
@@ -17158,9 +17158,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM35" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AM35" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="AN35" s="6" t="inlineStr">

--- a/product_selector_out/STM32L4x2.xlsx
+++ b/product_selector_out/STM32L4x2.xlsx
@@ -506,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BM35"/>
+  <dimension ref="A1:BN35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.3828125" customWidth="1" min="1" max="1"/>
@@ -573,7 +573,8 @@
     <col width="21.765625" customWidth="1" min="62" max="62"/>
     <col width="18" customWidth="1" min="63" max="63"/>
     <col width="18" customWidth="1" min="64" max="64"/>
-    <col width="52" customWidth="1" min="65" max="65"/>
+    <col width="18" customWidth="1" min="65" max="65"/>
+    <col width="52" customWidth="1" min="66" max="66"/>
   </cols>
   <sheetData>
     <row r="1"/>
@@ -901,6 +902,11 @@
         </is>
       </c>
       <c r="BM10" s="2" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="BN10" s="2" t="inlineStr">
         <is>
           <t>Datasheet URL</t>
         </is>
@@ -996,6 +1002,7 @@
       <c r="BK11" s="2" t="n"/>
       <c r="BL11" s="2" t="n"/>
       <c r="BM11" s="2" t="n"/>
+      <c r="BN11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -1320,6 +1327,11 @@
       </c>
       <c r="BM12" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN12" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l442kc.pdf</t>
         </is>
       </c>
@@ -1647,6 +1659,11 @@
       </c>
       <c r="BM13" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN13" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l412c8.pdf</t>
         </is>
       </c>
@@ -1974,6 +1991,11 @@
       </c>
       <c r="BM14" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN14" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l422cb.pdf</t>
         </is>
       </c>
@@ -2301,6 +2323,11 @@
       </c>
       <c r="BM15" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN15" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l462ce.pdf</t>
         </is>
       </c>
@@ -2628,6 +2655,11 @@
       </c>
       <c r="BM16" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN16" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l412c8.pdf</t>
         </is>
       </c>
@@ -2955,6 +2987,11 @@
       </c>
       <c r="BM17" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN17" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l412c8.pdf</t>
         </is>
       </c>
@@ -3282,6 +3319,11 @@
       </c>
       <c r="BM18" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN18" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l412c8.pdf</t>
         </is>
       </c>
@@ -3609,6 +3651,11 @@
       </c>
       <c r="BM19" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN19" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l462ce.pdf</t>
         </is>
       </c>
@@ -3936,6 +3983,11 @@
       </c>
       <c r="BM20" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN20" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l452cc.pdf</t>
         </is>
       </c>
@@ -4263,6 +4315,11 @@
       </c>
       <c r="BM21" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN21" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l432kb.pdf</t>
         </is>
       </c>
@@ -4590,6 +4647,11 @@
       </c>
       <c r="BM22" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN22" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l452cc.pdf</t>
         </is>
       </c>
@@ -4917,6 +4979,11 @@
       </c>
       <c r="BM23" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN23" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l462ce.pdf</t>
         </is>
       </c>
@@ -5244,6 +5311,11 @@
       </c>
       <c r="BM24" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN24" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l422cb.pdf</t>
         </is>
       </c>
@@ -5571,6 +5643,11 @@
       </c>
       <c r="BM25" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN25" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l452cc.pdf</t>
         </is>
       </c>
@@ -5898,6 +5975,11 @@
       </c>
       <c r="BM26" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN26" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l422cb.pdf</t>
         </is>
       </c>
@@ -6225,6 +6307,11 @@
       </c>
       <c r="BM27" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN27" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l412c8.pdf</t>
         </is>
       </c>
@@ -6552,6 +6639,11 @@
       </c>
       <c r="BM28" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN28" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l452cc.pdf</t>
         </is>
       </c>
@@ -6879,6 +6971,11 @@
       </c>
       <c r="BM29" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN29" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l412c8.pdf</t>
         </is>
       </c>
@@ -7206,6 +7303,11 @@
       </c>
       <c r="BM30" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN30" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l412c8.pdf</t>
         </is>
       </c>
@@ -7533,6 +7635,11 @@
       </c>
       <c r="BM31" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN31" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l432kb.pdf</t>
         </is>
       </c>
@@ -7860,6 +7967,11 @@
       </c>
       <c r="BM32" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN32" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l452cc.pdf</t>
         </is>
       </c>
@@ -8187,6 +8299,11 @@
       </c>
       <c r="BM33" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN33" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l452cc.pdf</t>
         </is>
       </c>
@@ -8514,6 +8631,11 @@
       </c>
       <c r="BM34" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN34" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l412c8.pdf</t>
         </is>
       </c>
@@ -8841,12 +8963,17 @@
       </c>
       <c r="BM35" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN35" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l422cb.pdf</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="64">
+  <mergeCells count="65">
     <mergeCell ref="P10:P11"/>
     <mergeCell ref="AS10:AS11"/>
     <mergeCell ref="AD10:AD11"/>
@@ -8867,16 +8994,14 @@
     <mergeCell ref="BA10:BA11"/>
     <mergeCell ref="BG10:BG11"/>
     <mergeCell ref="Q10:Q11"/>
-    <mergeCell ref="A1:BM8"/>
     <mergeCell ref="AR10:AR11"/>
+    <mergeCell ref="AT10:AT11"/>
     <mergeCell ref="S10:S11"/>
-    <mergeCell ref="AT10:AT11"/>
+    <mergeCell ref="BI10:BI11"/>
     <mergeCell ref="AV10:AV11"/>
-    <mergeCell ref="A9:BM9"/>
     <mergeCell ref="BB10:BB11"/>
-    <mergeCell ref="BI10:BI11"/>
+    <mergeCell ref="BM10:BM11"/>
     <mergeCell ref="BD10:BD11"/>
-    <mergeCell ref="BM10:BM11"/>
     <mergeCell ref="Y10:Z10"/>
     <mergeCell ref="AC10:AC11"/>
     <mergeCell ref="B10:B11"/>
@@ -8889,6 +9014,7 @@
     <mergeCell ref="AQ10:AQ11"/>
     <mergeCell ref="AW10:AW11"/>
     <mergeCell ref="BH10:BH11"/>
+    <mergeCell ref="BN10:BN11"/>
     <mergeCell ref="AY10:AY11"/>
     <mergeCell ref="BK10:BK11"/>
     <mergeCell ref="A10:A11"/>
@@ -8908,7 +9034,9 @@
     <mergeCell ref="U10:V10"/>
     <mergeCell ref="AG10:AG11"/>
     <mergeCell ref="F10:F11"/>
+    <mergeCell ref="A9:BN9"/>
     <mergeCell ref="H10:H11"/>
+    <mergeCell ref="A1:BN8"/>
     <mergeCell ref="T10:T11"/>
     <mergeCell ref="J10:J11"/>
   </mergeCells>
@@ -8949,7 +9077,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BM35"/>
+  <dimension ref="A1:BN35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -9017,6 +9145,7 @@
     <col width="16" customWidth="1" min="63" max="63"/>
     <col width="16" customWidth="1" min="64" max="64"/>
     <col width="16" customWidth="1" min="65" max="65"/>
+    <col width="16" customWidth="1" min="66" max="66"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -9350,6 +9479,11 @@
         </is>
       </c>
       <c r="BM10" s="2" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="BN10" s="2" t="inlineStr">
         <is>
           <t>Datasheet URL</t>
         </is>
@@ -9445,6 +9579,7 @@
       <c r="BK11" s="2" t="n"/>
       <c r="BL11" s="2" t="n"/>
       <c r="BM11" s="2" t="n"/>
+      <c r="BN11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -9767,7 +9902,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM12" s="6" t="inlineStr">
+      <c r="BM12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN12" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -10094,7 +10234,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM13" s="6" t="inlineStr">
+      <c r="BM13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN13" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -10421,7 +10566,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM14" s="6" t="inlineStr">
+      <c r="BM14" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN14" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -10748,7 +10898,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM15" s="6" t="inlineStr">
+      <c r="BM15" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN15" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -11075,7 +11230,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM16" s="6" t="inlineStr">
+      <c r="BM16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN16" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -11402,7 +11562,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM17" s="6" t="inlineStr">
+      <c r="BM17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN17" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -11729,7 +11894,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM18" s="6" t="inlineStr">
+      <c r="BM18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN18" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -12056,7 +12226,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM19" s="6" t="inlineStr">
+      <c r="BM19" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN19" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -12383,7 +12558,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM20" s="6" t="inlineStr">
+      <c r="BM20" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN20" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -12710,7 +12890,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM21" s="6" t="inlineStr">
+      <c r="BM21" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN21" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -13037,7 +13222,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM22" s="6" t="inlineStr">
+      <c r="BM22" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN22" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -13364,7 +13554,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM23" s="6" t="inlineStr">
+      <c r="BM23" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN23" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -13691,7 +13886,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM24" s="6" t="inlineStr">
+      <c r="BM24" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN24" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -14018,7 +14218,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM25" s="6" t="inlineStr">
+      <c r="BM25" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN25" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -14345,7 +14550,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM26" s="6" t="inlineStr">
+      <c r="BM26" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN26" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -14672,7 +14882,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM27" s="6" t="inlineStr">
+      <c r="BM27" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN27" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -14999,7 +15214,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM28" s="6" t="inlineStr">
+      <c r="BM28" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN28" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -15326,7 +15546,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM29" s="6" t="inlineStr">
+      <c r="BM29" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN29" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -15653,7 +15878,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM30" s="6" t="inlineStr">
+      <c r="BM30" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN30" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -15980,7 +16210,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM31" s="6" t="inlineStr">
+      <c r="BM31" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN31" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -16307,7 +16542,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM32" s="6" t="inlineStr">
+      <c r="BM32" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN32" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -16634,7 +16874,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM33" s="6" t="inlineStr">
+      <c r="BM33" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN33" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -16961,7 +17206,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM34" s="6" t="inlineStr">
+      <c r="BM34" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN34" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -17288,7 +17538,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM35" s="6" t="inlineStr">
+      <c r="BM35" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN35" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -17296,8 +17551,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A9:BM9"/>
-    <mergeCell ref="A1:BM8"/>
+    <mergeCell ref="A9:BN9"/>
+    <mergeCell ref="A1:BN8"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
